--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T15:25:29+00:00</t>
+    <t>2024-10-26T11:41:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T11:41:35+00:00</t>
+    <t>2024-10-26T12:52:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:52:52+00:00</t>
+    <t>2024-10-26T13:45:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:45:19+00:00</t>
+    <t>2024-10-26T13:53:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:53:56+00:00</t>
+    <t>2024-10-31T15:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:15:50+00:00</t>
+    <t>2024-11-17T20:36:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:36:22+00:00</t>
+    <t>2024-11-17T21:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:00:03+00:00</t>
+    <t>2024-11-17T21:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:23:25+00:00</t>
+    <t>2024-11-27T13:38:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:38:13+00:00</t>
+    <t>2024-12-15T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T13:48:39+00:00</t>
+    <t>2024-12-19T09:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5601,7 +5601,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="428">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-19T09:41:53+00:00</t>
+    <t>2025-01-08T15:19:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1068,95 +1068,92 @@
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+    <t>Address(es) of the practitioner that are not role specific (typically home address)</t>
+  </si>
+  <si>
+    <t>Address(es) of the practitioner that are not role specific (typically home address). +Work addresses are not typically entered in this property as they are usually role dependent.</t>
+  </si>
+  <si>
+    <t>The PractitionerRole does not have an address value on it, as it is expected that the location property be used for this purpose (which has an address).</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
+  </si>
+  <si>
+    <t>ORC-24, STF-11, ROL-11, PRT-14</t>
+  </si>
+  <si>
+    <t>./addr</t>
+  </si>
+  <si>
+    <t>./Addresses</t>
+  </si>
+  <si>
+    <t>Practitioner.gender</t>
+  </si>
+  <si>
+    <t>male | female | other | unknown</t>
+  </si>
+  <si>
+    <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
+  </si>
+  <si>
+    <t>Needed to address the person correctly.</t>
+  </si>
+  <si>
+    <t>The gender of a person used for administrative purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+  </si>
+  <si>
+    <t>STF-5</t>
+  </si>
+  <si>
+    <t>./administrativeGender</t>
+  </si>
+  <si>
+    <t>./GenderCode</t>
+  </si>
+  <si>
+    <t>Practitioner.gender.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Practitioner.gender.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Practitioner.gender.extension:AdministrativeGenderAddition</t>
+  </si>
+  <si>
+    <t>AdministrativeGenderAddition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
+</t>
+  </si>
+  <si>
+    <t>Administrative Gender Addition</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the administrative gender of a person (Patient, Practitioner, ...). 
+The extension is used to add the missing codes and is applied in case the code for administrative gender itself is set to 'other'.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
-  </si>
-  <si>
-    <t>XAD</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Practitioner.gender</t>
-  </si>
-  <si>
-    <t>male | female | other | unknown</t>
-  </si>
-  <si>
-    <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
-  </si>
-  <si>
-    <t>Needed to address the person correctly.</t>
-  </si>
-  <si>
-    <t>The gender of a person used for administrative purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
-  </si>
-  <si>
-    <t>STF-5</t>
-  </si>
-  <si>
-    <t>./administrativeGender</t>
-  </si>
-  <si>
-    <t>./GenderCode</t>
-  </si>
-  <si>
-    <t>Practitioner.gender.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Practitioner.gender.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Practitioner.gender.extension:AdministrativeGenderAddition</t>
-  </si>
-  <si>
-    <t>AdministrativeGenderAddition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
-</t>
-  </si>
-  <si>
-    <t>Administrative Gender Addition</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the administrative gender of a person (Patient, Practitioner, ...). 
-The extension is used to add the missing codes and is applied in case the code for administrative gender itself is set to 'other'.</t>
   </si>
   <si>
     <t>Practitioner.gender.value</t>
@@ -1695,7 +1692,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="31.08984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -9382,7 +9379,7 @@
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>337</v>
@@ -9455,19 +9452,19 @@
         <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK68" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AJ68" t="s" s="2">
+      <c r="AL68" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AK68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9475,10 +9472,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9504,14 +9501,14 @@
         <v>108</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9539,10 +9536,10 @@
         <v>172</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9560,7 +9557,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9575,13 +9572,13 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9589,10 +9586,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9618,10 +9615,10 @@
         <v>157</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9701,10 +9698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9730,10 +9727,10 @@
         <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9811,13 +9808,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>21</v>
@@ -9839,13 +9836,13 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9905,7 +9902,7 @@
         <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>139</v>
@@ -9925,10 +9922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9954,10 +9951,10 @@
         <v>157</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10008,7 +10005,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10037,10 +10034,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10063,17 +10060,17 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10122,7 +10119,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10137,13 +10134,13 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10151,10 +10148,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10177,17 +10174,17 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10236,7 +10233,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10254,10 +10251,10 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10265,10 +10262,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10291,13 +10288,13 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10348,7 +10345,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10363,13 +10360,13 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AM76" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10377,10 +10374,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10489,10 +10486,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10603,14 +10600,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10632,10 +10629,10 @@
         <v>134</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>137</v>
@@ -10690,7 +10687,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10719,10 +10716,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10748,14 +10745,14 @@
         <v>146</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -10804,7 +10801,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10822,7 +10819,7 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
@@ -10833,10 +10830,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10862,10 +10859,10 @@
         <v>178</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10892,14 +10889,14 @@
         <v>21</v>
       </c>
       <c r="X81" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Y81" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Y81" t="s" s="2">
+      <c r="Z81" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="Z81" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="AA81" t="s" s="2">
         <v>21</v>
       </c>
@@ -10916,7 +10913,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>88</v>
@@ -10934,10 +10931,10 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -10945,10 +10942,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10974,14 +10971,14 @@
         <v>207</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11030,7 +11027,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11048,10 +11045,10 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -11059,10 +11056,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11088,10 +11085,10 @@
         <v>215</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11142,7 +11139,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11160,7 +11157,7 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
@@ -11171,10 +11168,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11200,16 +11197,16 @@
         <v>178</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11258,7 +11255,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11273,13 +11270,13 @@
         <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL84" t="s" s="2">
+      <c r="AM84" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T15:19:00+00:00</t>
+    <t>2025-01-24T15:25:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:25:06+00:00</t>
+    <t>2025-01-27T07:42:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T07:42:42+00:00</t>
+    <t>2025-01-27T10:22:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T10:22:54+00:00</t>
+    <t>2025-01-27T12:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-01T11:26:35+00:00</t>
+    <t>2026-08-11T10:57:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:57:38+00:00</t>
+    <t>2026-08-11T12:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1058,7 +1058,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address}
+    <t xml:space="preserve">Address {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address}
 </t>
   </si>
   <si>
@@ -1135,7 +1135,7 @@
     <t>AdministrativeGenderAddition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
 </t>
   </si>
   <si>
@@ -1661,7 +1661,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="98.24609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="85.5859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T12:53:53+00:00</t>
+    <t>2026-08-20T09:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
